--- a/VerveStacks_MYS_grids_kan/vt_vervestacks_MYS_v1.xlsx
+++ b/VerveStacks_MYS_grids_kan/vt_vervestacks_MYS_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_MYS_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3BA34EB-41A7-4684-8224-487567B25083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1BF98F2E-5257-4464-8470-FCB820C49ECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{07BF5413-2B6D-4360-991D-4ADDFCB14609}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{E930C3DB-F804-4E32-AA72-92FDF3BCFA98}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -1930,7 +1930,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51D86CF4-BB2E-4470-B875-526B2562104C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD4A53E-8841-4F3E-A0EC-3DC1AEBF830C}">
   <dimension ref="B9:V84"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -6598,7 +6598,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DC72B0F-37F8-466D-927A-596BA2E494CE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA1D3ECD-82CB-4F08-9C90-6C80A06B0C06}">
   <dimension ref="B9:V39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -8404,7 +8404,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7335F23B-19C5-4E9A-B9F3-6CB2551948B5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{158E4ED0-14E8-4D51-9778-D6542198A397}">
   <dimension ref="B9:V170"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -14032,7 +14032,7 @@
         <v>33</v>
       </c>
       <c r="M105">
-        <v>0.18283805895154923</v>
+        <v>0.18283805895154917</v>
       </c>
       <c r="O105" t="s">
         <v>196</v>
@@ -14085,7 +14085,7 @@
         <v>33</v>
       </c>
       <c r="M106">
-        <v>0.18283805895154923</v>
+        <v>0.18283805895154917</v>
       </c>
       <c r="O106" t="s">
         <v>196</v>
@@ -14138,7 +14138,7 @@
         <v>33</v>
       </c>
       <c r="M107">
-        <v>0.18283805895154923</v>
+        <v>0.18283805895154917</v>
       </c>
       <c r="O107" t="s">
         <v>196</v>
@@ -15018,7 +15018,7 @@
         <v>14</v>
       </c>
       <c r="R121" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="S121" t="s">
         <v>198</v>
@@ -15080,7 +15080,7 @@
         <v>14</v>
       </c>
       <c r="R122" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="S122" t="s">
         <v>198</v>
@@ -17045,7 +17045,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6280328-084D-417A-B973-90E2182672F9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8842CD2C-B51C-48B7-9A02-A618E530D01C}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
